--- a/Result/profitability/4735.xlsx
+++ b/Result/profitability/4735.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM70"/>
+  <dimension ref="A1:AM71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-1.03</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4675</v>
+        <v>0.7949999999999999</v>
       </c>
       <c r="N2" t="n">
-        <v>30.55375</v>
+        <v>30.11375</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-0.28</v>
       </c>
       <c r="M3" t="n">
-        <v>0.3625</v>
+        <v>0.6875</v>
       </c>
       <c r="N3" t="n">
-        <v>29.49875</v>
+        <v>29.3725</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.06</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2975</v>
+        <v>0.6587500000000001</v>
       </c>
       <c r="N4" t="n">
-        <v>29.225</v>
+        <v>29.08</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>2.25</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5425</v>
+        <v>0.87625</v>
       </c>
       <c r="N5" t="n">
-        <v>30.6975</v>
+        <v>30.44875</v>
       </c>
       <c r="O5" t="n">
         <v>1</v>
@@ -1030,7 +1030,7 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
         <v>1</v>
@@ -1039,7 +1039,7 @@
         <v>1</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
         <v>0</v>
@@ -1137,13 +1137,13 @@
         <v>0.55</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5475</v>
+        <v>0.8325</v>
       </c>
       <c r="N6" t="n">
-        <v>30.50875</v>
+        <v>29.9775</v>
       </c>
       <c r="O6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
         <v>1</v>
@@ -1155,7 +1155,7 @@
         <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1264,13 +1264,13 @@
         <v>0.7</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5225</v>
+        <v>0.8275</v>
       </c>
       <c r="N7" t="n">
-        <v>32.73</v>
+        <v>32.61875</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>1</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>-0.03</v>
       </c>
       <c r="M8" t="n">
-        <v>0.42625</v>
+        <v>0.6749999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>29.41375</v>
+        <v>28.96</v>
       </c>
       <c r="O8" t="n">
         <v>0</v>
@@ -9318,6 +9318,133 @@
       </c>
       <c r="AM70" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>4735</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>273</v>
+      </c>
+      <c r="D71" t="n">
+        <v>193</v>
+      </c>
+      <c r="E71" t="n">
+        <v>81</v>
+      </c>
+      <c r="F71" t="n">
+        <v>29.49</v>
+      </c>
+      <c r="G71" t="n">
+        <v>28</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>10.37%</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>102</v>
+      </c>
+      <c r="J71" t="n">
+        <v>130</v>
+      </c>
+      <c r="K71" t="n">
+        <v>122</v>
+      </c>
+      <c r="L71" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.99375</v>
+      </c>
+      <c r="N71" t="n">
+        <v>31.54625</v>
+      </c>
+      <c r="O71" t="n">
+        <v>1</v>
+      </c>
+      <c r="P71" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>1</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
+      </c>
+      <c r="V71" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W71" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="X71" t="n">
+        <v>1.672268907563025</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>-3.629999999999999</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>-0.1096014492753623</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>5.235294117647059</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>-1.990000000000002</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>-0.06321473951715384</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK71" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
